--- a/output/graficos_regionales_migracion/plot_migracion_miginterna_2021_magallanes_grupos.xlsx
+++ b/output/graficos_regionales_migracion/plot_migracion_miginterna_2021_magallanes_grupos.xlsx
@@ -72,7 +72,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-27 23:14</t>
+    <t xml:space="preserve">2026-09-29 14:12</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_migracion/plot_migracion_miginterna_2021_magallanes_grupos.xlsx
+++ b/output/graficos_regionales_migracion/plot_migracion_miginterna_2021_magallanes_grupos.xlsx
@@ -72,7 +72,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-29 14:12</t>
+    <t xml:space="preserve">2026-09-29 18:41</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_migracion/plot_migracion_miginterna_2021_magallanes_grupos.xlsx
+++ b/output/graficos_regionales_migracion/plot_migracion_miginterna_2021_magallanes_grupos.xlsx
@@ -72,7 +72,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-29 18:41</t>
+    <t xml:space="preserve">2026-10-05 04:06</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
